--- a/02_Glider_Design/C_results/nausicaa_results_iter5.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results_iter5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hl3422_ic_ac_uk/Documents/Year 4/Final Year Project/01 - Github/Nausicaa/02_Glider_Design/C_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_F85747D6B5C4E787C875B9239F204A9A932CC91D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{137795A7-EBBA-4A3C-8760-6513B9E9E442}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_F85747D6B5C4E787C875B9239F204A9A932CC91D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F3DBDB-AC11-47A9-B2AB-1BA84EE26D3B}"/>
   <bookViews>
-    <workbookView xWindow="21840" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4670" yWindow="2360" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="ObjectiveTerms" sheetId="8" r:id="rId8"/>
     <sheet name="DesignVarBounds" sheetId="9" r:id="rId9"/>
     <sheet name="DesignPoints" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -2050,6 +2051,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3824,6 +3826,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="32.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -4318,6 +4323,16 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6615ED9C-997D-43CE-ABE7-3C4638411240}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5506,6 +5521,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">

--- a/02_Glider_Design/C_results/nausicaa_results_iter5.xlsx
+++ b/02_Glider_Design/C_results/nausicaa_results_iter5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/hl3422_ic_ac_uk/Documents/Year 4/Final Year Project/01 - Github/Nausicaa/02_Glider_Design/C_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_F85747D6B5C4E787C875B9239F204A9A932CC91D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F3DBDB-AC11-47A9-B2AB-1BA84EE26D3B}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_F85747D6B5C4E787C875B9239F204A9A932CC91D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA8B2E36-AAD5-4D6E-B13B-99D58725FFDD}"/>
   <bookViews>
-    <workbookView xWindow="4670" yWindow="2360" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -23,14 +23,26 @@
     <sheet name="ObjectiveTerms" sheetId="8" r:id="rId8"/>
     <sheet name="DesignVarBounds" sheetId="9" r:id="rId9"/>
     <sheet name="DesignPoints" sheetId="10" r:id="rId10"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="662">
   <si>
     <t>Metric</t>
   </si>
@@ -515,9 +527,6 @@
     <t>htail_span_m</t>
   </si>
   <si>
-    <t>htail_chord_m</t>
-  </si>
-  <si>
     <t>htail_area_m2</t>
   </si>
   <si>
@@ -528,9 +537,6 @@
   </si>
   <si>
     <t>vtail_area_m2</t>
-  </si>
-  <si>
-    <t>dihedral_deg</t>
   </si>
   <si>
     <t>aileron_semispan_start</t>
@@ -2033,6 +2039,34 @@
   </si>
   <si>
     <t>CL_turn</t>
+  </si>
+  <si>
+    <t>dihedral_deg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>m</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>htail_chord_m</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>htail_span_m</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wing_AC_m</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>htail_AC_m</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>vtail_AC_m</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2409,6 +2443,7 @@
   <cols>
     <col min="1" max="1" width="22.90625" customWidth="1"/>
     <col min="2" max="2" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3832,7 +3867,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3846,10 +3881,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C2">
         <v>6.5</v>
@@ -3860,10 +3895,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>639</v>
+      </c>
+      <c r="B3" t="s">
         <v>641</v>
-      </c>
-      <c r="B3" t="s">
-        <v>643</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -3874,10 +3909,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C4">
         <v>50</v>
@@ -3888,10 +3923,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B5" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C5">
         <v>0.2</v>
@@ -3902,10 +3937,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B6" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C6">
         <v>0.2</v>
@@ -3916,10 +3951,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B7" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C7">
         <v>8.4</v>
@@ -3930,10 +3965,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>645</v>
+      </c>
+      <c r="B8" t="s">
         <v>647</v>
-      </c>
-      <c r="B8" t="s">
-        <v>649</v>
       </c>
       <c r="C8">
         <v>4.8</v>
@@ -3944,10 +3979,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B9" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C9">
         <v>3.5</v>
@@ -3958,10 +3993,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B10" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C10">
         <v>3.8080354659860869</v>
@@ -3972,10 +4007,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C11">
         <v>7.8653558859592498E-15</v>
@@ -3986,10 +4021,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B12" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C12">
         <v>-0.1140304863710548</v>
@@ -4000,10 +4035,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B13" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C13">
         <v>-1.367107440935978E-14</v>
@@ -4014,10 +4049,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B14" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C14">
         <v>0.67031355376587765</v>
@@ -4028,10 +4063,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>649</v>
+      </c>
+      <c r="B15" t="s">
         <v>651</v>
-      </c>
-      <c r="B15" t="s">
-        <v>653</v>
       </c>
       <c r="C15">
         <v>0.35532273919989299</v>
@@ -4042,10 +4077,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B16" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C16">
         <v>-0.82724261728227877</v>
@@ -4056,7 +4091,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -4070,7 +4105,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -4084,7 +4119,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
@@ -4098,7 +4133,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B20" t="s">
         <v>29</v>
@@ -4112,10 +4147,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B21" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C21">
         <v>0.35532273919989299</v>
@@ -4126,7 +4161,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B22" t="s">
         <v>52</v>
@@ -4140,7 +4175,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B23" t="s">
         <v>53</v>
@@ -4154,7 +4189,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B24" t="s">
         <v>54</v>
@@ -4168,7 +4203,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B25" t="s">
         <v>56</v>
@@ -4182,7 +4217,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B26" t="s">
         <v>57</v>
@@ -4196,7 +4231,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B27" t="s">
         <v>58</v>
@@ -4210,7 +4245,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B28" t="s">
         <v>59</v>
@@ -4224,10 +4259,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B29" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C29">
         <v>-0.82724261728227877</v>
@@ -4238,7 +4273,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B30" t="s">
         <v>71</v>
@@ -4252,7 +4287,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B31" t="s">
         <v>72</v>
@@ -4266,7 +4301,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B32" t="s">
         <v>73</v>
@@ -4280,7 +4315,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B33" t="s">
         <v>74</v>
@@ -4294,7 +4329,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B34" t="s">
         <v>75</v>
@@ -4308,7 +4343,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B35" t="s">
         <v>76</v>
@@ -4326,23 +4361,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6615ED9C-997D-43CE-ABE7-3C4638411240}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.08984375" customWidth="1"/>
     <col min="2" max="2" width="9.1796875" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4435,7 +4461,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>658</v>
       </c>
       <c r="B9">
         <v>0.36555216483528957</v>
@@ -4446,7 +4472,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>657</v>
       </c>
       <c r="B10">
         <v>9.1388041208822393E-2</v>
@@ -4457,7 +4483,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B11">
         <v>3.3407096303941682E-2</v>
@@ -4468,7 +4494,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B12">
         <v>0.1187676990826549</v>
@@ -4479,7 +4505,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B13">
         <v>5.9383849541327451E-2</v>
@@ -4490,7 +4516,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B14">
         <v>7.0528831726940329E-3</v>
@@ -4501,7 +4527,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>166</v>
+        <v>655</v>
       </c>
       <c r="B15">
         <v>10</v>
@@ -4512,35 +4538,71 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B16">
         <v>0.3</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B17">
         <v>0.85</v>
       </c>
       <c r="C17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B18">
         <v>0.3</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>659</v>
+      </c>
+      <c r="B19">
+        <f>0.25*B3</f>
+        <v>4.1159917649024297E-2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>660</v>
+      </c>
+      <c r="B20">
+        <f>B7-0.7*B10+0.25*B10</f>
+        <v>0.42284700470709119</v>
+      </c>
+      <c r="C20" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>661</v>
+      </c>
+      <c r="B21">
+        <f>B7-0.7*B10+(0.3*B10-0.3*B13)+0.25*B13</f>
+        <v>0.42444721429046595</v>
+      </c>
+      <c r="C21" t="s">
+        <v>656</v>
       </c>
     </row>
   </sheetData>
@@ -4556,36 +4618,36 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B2">
         <v>2.4826156428088889E-2</v>
@@ -4614,7 +4676,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B3">
         <v>1.198624513657535E-2</v>
@@ -4643,7 +4705,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B4">
         <v>8.7055664260307451E-3</v>
@@ -4672,7 +4734,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B5">
         <v>7.4414302554423094E-3</v>
@@ -4701,7 +4763,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B6">
         <v>6.0000000000000001E-3</v>
@@ -4730,7 +4792,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B7">
         <v>5.7726765586662418E-3</v>
@@ -4759,7 +4821,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B8">
         <v>5.0000000000000001E-3</v>
@@ -4788,7 +4850,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B9">
         <v>4.0088515564730021E-3</v>
@@ -4817,7 +4879,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B10">
         <v>4.0000000000000001E-3</v>
@@ -4846,7 +4908,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B11">
         <v>4.0000000000000001E-3</v>
@@ -4875,7 +4937,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B12">
         <v>4.0000000000000001E-3</v>
@@ -4904,7 +4966,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B13">
         <v>4.0000000000000001E-3</v>
@@ -4933,7 +4995,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B14">
         <v>3.8544401873137498E-3</v>
@@ -4962,7 +5024,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B15">
         <v>3.8544401873137498E-3</v>
@@ -4991,7 +5053,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B16">
         <v>3.8544401873137498E-3</v>
@@ -5020,7 +5082,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B17">
         <v>3.8544401873137498E-3</v>
@@ -5049,7 +5111,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B18">
         <v>1.7952908587257621E-3</v>
@@ -5078,7 +5140,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B19">
         <v>1.3125000131177769E-3</v>
@@ -5107,7 +5169,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B20">
         <v>1.3125000131177769E-3</v>
@@ -5136,7 +5198,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B21">
         <v>1E-3</v>
@@ -5165,7 +5227,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B22">
         <v>1E-3</v>
@@ -5194,7 +5256,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B23">
         <v>1E-3</v>
@@ -5223,7 +5285,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B24">
         <v>8.4634598072328392E-4</v>
@@ -5252,7 +5314,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B25">
         <v>7.6288088642659289E-4</v>
@@ -5281,7 +5343,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B26">
         <v>7.6288088642659289E-4</v>
@@ -5310,7 +5372,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B27">
         <v>6.7894736842105251E-4</v>
@@ -5339,7 +5401,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B28">
         <v>6.3971628846175668E-4</v>
@@ -5368,7 +5430,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B29">
         <v>6.3971628846175668E-4</v>
@@ -5397,7 +5459,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B30">
         <v>5.9599411416964712E-4</v>
@@ -5426,7 +5488,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B31">
         <v>2.0784347339464611E-4</v>
@@ -5455,7 +5517,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B32">
         <v>2.0784347339464611E-4</v>
@@ -5484,7 +5546,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B33">
         <v>-3.9600000395782081E-4</v>
@@ -5527,7 +5589,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5535,7 +5597,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B2">
         <v>3.6642715401622207E-2</v>
@@ -5543,7 +5605,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B3">
         <v>0.70615590458660793</v>
@@ -5551,7 +5613,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B4">
         <v>-2.282843122620439E-8</v>
@@ -5559,7 +5621,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B5">
         <v>-1.7946609442986981E-3</v>
@@ -5567,7 +5629,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B6">
         <v>7.1601275849923762E-2</v>
@@ -5575,7 +5637,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B7">
         <v>-7.7632318046250148E-5</v>
@@ -5583,7 +5645,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B8">
         <v>0.35532273919989299</v>
@@ -5591,7 +5653,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B9">
         <v>5.648463391351588</v>
@@ -5599,7 +5661,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B10">
         <v>-2.191039274239208E-5</v>
@@ -5607,7 +5669,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B11">
         <v>-1.250308513706111E-2</v>
@@ -5615,7 +5677,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B12">
         <v>0.93233362775518858</v>
@@ -5623,7 +5685,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B13">
         <v>-2.424221027252926E-4</v>
@@ -5631,7 +5693,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B14">
         <v>-6.0043849355593931E-17</v>
@@ -5639,7 +5701,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B15">
         <v>5.5444013263686612E-12</v>
@@ -5647,7 +5709,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B16">
         <v>-0.2408579823093662</v>
@@ -5655,7 +5717,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B17">
         <v>-0.40003159925023818</v>
@@ -5663,7 +5725,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B18">
         <v>4.5967301760848649E-14</v>
@@ -5671,7 +5733,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B19">
         <v>0.10240214304463879</v>
@@ -5679,7 +5741,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B20">
         <v>-1.449605514745473E-16</v>
@@ -5687,7 +5749,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B21">
         <v>1.029689396391938E-11</v>
@@ -5695,7 +5757,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B22">
         <v>-0.1986060691007141</v>
@@ -5703,7 +5765,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B23">
         <v>-0.7794457260989065</v>
@@ -5711,7 +5773,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B24">
         <v>1.081083517758276E-13</v>
@@ -5719,7 +5781,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B25">
         <v>1.5913714763323639E-2</v>
@@ -5727,7 +5789,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B26">
         <v>-1.009957488131532E-6</v>
@@ -5735,7 +5797,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B27">
         <v>-0.56484639518789748</v>
@@ -5743,7 +5805,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B28">
         <v>-5.7832124169520329E-6</v>
@@ -5751,7 +5813,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B29">
         <v>-3.253733018465601E-3</v>
@@ -5759,7 +5821,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B30">
         <v>-11.474722387417311</v>
@@ -5767,7 +5829,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B31">
         <v>-1.2671924785283471E-4</v>
@@ -5775,7 +5837,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B32">
         <v>-1.5253314907017229E-17</v>
@@ -5783,7 +5845,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B33">
         <v>1.0608616341383131E-12</v>
@@ -5791,7 +5853,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B34">
         <v>2.574590957155478E-2</v>
@@ -5799,7 +5861,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B35">
         <v>-8.4930584757334546E-2</v>
@@ -5807,7 +5869,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B36">
         <v>8.165262820429911E-15</v>
@@ -5815,7 +5877,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B37">
         <v>-4.8544405945456962E-2</v>
@@ -5823,7 +5885,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B38">
         <v>0.1188952361523956</v>
@@ -5831,7 +5893,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B39">
         <v>3.5998293204875402E-2</v>
@@ -5839,7 +5901,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B40">
         <v>8.2896942947520244E-2</v>
@@ -5847,7 +5909,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B41">
         <v>-4.2062782734785233E-2</v>
@@ -5855,7 +5917,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B42">
         <v>4.2062782734785233E-2</v>
@@ -5863,7 +5925,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B43">
         <v>-0.1188952361523956</v>
@@ -5871,7 +5933,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B44">
         <v>1.152921679642144</v>
@@ -5879,7 +5941,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B45">
         <v>-3.5820896067059098E-16</v>
@@ -5887,7 +5949,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B46">
         <v>3.5820896067059098E-16</v>
@@ -5895,7 +5957,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B47">
         <v>-3.5992137393034749E-16</v>
@@ -5903,7 +5965,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B48">
         <v>-1.948252898396324E-16</v>
@@ -5911,15 +5973,15 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B49" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B50">
         <v>-3.5820896067059098E-16</v>
@@ -5927,7 +5989,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B51">
         <v>-5.3952849453538232E-7</v>
@@ -5935,7 +5997,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B52">
         <v>-3.7692144683812443E-17</v>
@@ -5943,15 +6005,15 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B53" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B54">
         <v>0.13020011811289969</v>
@@ -5959,7 +6021,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B55">
         <v>0.19514225978621841</v>
@@ -5967,7 +6029,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B56">
         <v>3.6642715401622207E-2</v>
@@ -5975,7 +6037,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B57">
         <v>0.70615590458660793</v>
@@ -5983,7 +6045,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B58">
         <v>-2.282843122620439E-8</v>
@@ -5991,7 +6053,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B59">
         <v>-1.7946609442986981E-3</v>
@@ -5999,7 +6061,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B60">
         <v>7.1601275849923762E-2</v>
@@ -6007,7 +6069,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B61">
         <v>-7.7632318046250148E-5</v>
@@ -6023,7 +6085,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B63">
         <v>5.648463391351588</v>
@@ -6031,7 +6093,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B64">
         <v>-2.191039274239208E-5</v>
@@ -6039,7 +6101,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B65">
         <v>-1.250308513706111E-2</v>
@@ -6047,7 +6109,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B66">
         <v>0.93233362775518858</v>
@@ -6055,7 +6117,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B67">
         <v>-2.424221027252926E-4</v>
@@ -6063,7 +6125,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B68">
         <v>-6.0043849355593931E-17</v>
@@ -6071,7 +6133,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B69">
         <v>5.5444013263686612E-12</v>
@@ -6079,7 +6141,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B70">
         <v>-0.2408579823093662</v>
@@ -6087,7 +6149,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B71">
         <v>-0.40003159925023818</v>
@@ -6095,7 +6157,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B72">
         <v>4.5967301760848649E-14</v>
@@ -6103,7 +6165,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B73">
         <v>0.10240214304463879</v>
@@ -6111,7 +6173,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B74">
         <v>-1.449605514745473E-16</v>
@@ -6119,7 +6181,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B75">
         <v>1.029689396391938E-11</v>
@@ -6127,7 +6189,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B76">
         <v>-0.1986060691007141</v>
@@ -6135,7 +6197,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B77">
         <v>-0.7794457260989065</v>
@@ -6143,7 +6205,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B78">
         <v>1.081083517758276E-13</v>
@@ -6151,7 +6213,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B79">
         <v>1.5913714763323639E-2</v>
@@ -6159,7 +6221,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B80">
         <v>-1.009957488131532E-6</v>
@@ -6167,7 +6229,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B81">
         <v>-0.56484639518789748</v>
@@ -6175,7 +6237,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B82">
         <v>-5.7832124169520329E-6</v>
@@ -6183,7 +6245,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B83">
         <v>-3.253733018465601E-3</v>
@@ -6191,7 +6253,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B84">
         <v>-11.474722387417311</v>
@@ -6199,7 +6261,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B85">
         <v>-1.2671924785283471E-4</v>
@@ -6207,7 +6269,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B86">
         <v>-1.5253314907017229E-17</v>
@@ -6215,7 +6277,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B87">
         <v>1.0608616341383131E-12</v>
@@ -6223,7 +6285,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B88">
         <v>2.574590957155478E-2</v>
@@ -6231,7 +6293,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B89">
         <v>-8.4930584757334546E-2</v>
@@ -6239,7 +6301,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B90">
         <v>8.165262820429911E-15</v>
@@ -6247,7 +6309,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B91">
         <v>-4.8544405945456962E-2</v>
@@ -6255,7 +6317,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B92">
         <v>0.1188952361523956</v>
@@ -6263,7 +6325,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B93">
         <v>3.5998293204875402E-2</v>
@@ -6271,7 +6333,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B94">
         <v>8.2896942947520244E-2</v>
@@ -6279,7 +6341,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B95">
         <v>-4.2062782734785233E-2</v>
@@ -6287,7 +6349,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B96">
         <v>4.2062782734785233E-2</v>
@@ -6295,7 +6357,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B97">
         <v>-0.1188952361523956</v>
@@ -6303,7 +6365,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B98">
         <v>1.152921679642144</v>
@@ -6311,7 +6373,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B99">
         <v>-3.5820896067059098E-16</v>
@@ -6319,7 +6381,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B100">
         <v>3.5820896067059098E-16</v>
@@ -6327,7 +6389,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B101">
         <v>-3.5992137393034749E-16</v>
@@ -6335,7 +6397,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B102">
         <v>-1.948252898396324E-16</v>
@@ -6343,15 +6405,15 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B103" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B104">
         <v>-3.5820896067059098E-16</v>
@@ -6359,7 +6421,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B105">
         <v>-5.3952849453538232E-7</v>
@@ -6367,7 +6429,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B106">
         <v>-3.7692144683812443E-17</v>
@@ -6375,15 +6437,15 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B107" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B108">
         <v>0.13020011811289969</v>
@@ -6391,7 +6453,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B109">
         <v>0.19514225978621841</v>
@@ -6410,51 +6472,51 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B2">
         <v>1.152921679642144</v>
@@ -6469,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H2">
         <v>-9.9892372151799691E-9</v>
@@ -6486,7 +6548,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B3">
         <v>0.1188952361523956</v>
@@ -6501,7 +6563,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H3">
         <v>0.1178952361523956</v>
@@ -6518,7 +6580,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B4">
         <v>-1.009957488131532E-6</v>
@@ -6536,7 +6598,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H4">
         <v>-9.9574881315319987E-9</v>
@@ -6556,7 +6618,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B5">
         <v>-1.449605514745473E-16</v>
@@ -6574,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H5">
         <v>-1.449605514745473E-16</v>
@@ -6600,7 +6662,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B6">
         <v>-1.5253314907017229E-17</v>
@@ -6618,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H6">
         <v>-1.5253314907017229E-17</v>
@@ -6644,7 +6706,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B7">
         <v>0.35532273919989299</v>
@@ -6659,7 +6721,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I7">
         <v>0.84467726080010697</v>
@@ -6676,7 +6738,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B8">
         <v>9.6969543688392257</v>
@@ -6691,7 +6753,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H8">
         <v>3.6969543688392261</v>
@@ -6708,7 +6770,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B9">
         <v>9.1950800039563934</v>
@@ -6723,7 +6785,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H9">
         <v>7.1950800039563934</v>
@@ -6740,7 +6802,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B10">
         <v>9.1950800039563934</v>
@@ -6755,7 +6817,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I10">
         <v>10.80491999604361</v>
@@ -6772,7 +6834,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B11">
         <v>73262.374121864079</v>
@@ -6787,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H11">
         <v>53262.374121864079</v>
@@ -6804,7 +6866,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B12">
         <v>0.10000000992353759</v>
@@ -6819,7 +6881,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H12">
         <v>5.000000992353755E-2</v>
@@ -6836,7 +6898,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B13">
         <v>0.10000000992353759</v>
@@ -6851,7 +6913,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I13">
         <v>-9.9235375472517262E-9</v>
@@ -6868,7 +6930,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B14">
         <v>0.64732134603071834</v>
@@ -6883,7 +6945,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H14">
         <v>0.14732134603071831</v>
@@ -6900,7 +6962,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B15">
         <v>0.64732134603071834</v>
@@ -6915,7 +6977,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I15">
         <v>0.35267865396928172</v>
@@ -6932,7 +6994,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B16">
         <v>2.999999002391656E-2</v>
@@ -6947,7 +7009,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H16">
         <v>-9.9760834385009822E-9</v>
@@ -6964,7 +7026,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B17">
         <v>2.999999002391656E-2</v>
@@ -6979,7 +7041,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I17">
         <v>5.0000009976083441E-2</v>
@@ -6996,7 +7058,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B18">
         <v>-0.1986060691007141</v>
@@ -7011,7 +7073,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I18">
         <v>0.1986060691007141</v>
@@ -7028,7 +7090,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B19">
         <v>2.574590957155478E-2</v>
@@ -7043,7 +7105,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H19">
         <v>2.574590957155478E-2</v>
@@ -7060,7 +7122,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B20">
         <v>-0.7794457260989065</v>
@@ -7075,7 +7137,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I20">
         <v>0.77934572609890651</v>
@@ -7092,7 +7154,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B21">
         <v>5.2397110819878439</v>
@@ -7104,7 +7166,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -7112,7 +7174,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B22">
         <v>229.06724327935751</v>
@@ -7124,7 +7186,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -7132,7 +7194,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B23">
         <v>2.2874117691274561E-2</v>
@@ -7144,7 +7206,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -7152,7 +7214,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B24">
         <v>3.461428953049963E-5</v>
@@ -7167,7 +7229,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I24">
         <v>7.1653857104694999E-3</v>
@@ -7184,7 +7246,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B25">
         <v>1.8615385756603531E-5</v>
@@ -7199,7 +7261,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I25">
         <v>7.1813846142433956E-3</v>
@@ -7216,7 +7278,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B26">
         <v>3.4759423022032989E-6</v>
@@ -7231,7 +7293,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I26">
         <v>7.1965240576977963E-3</v>
@@ -7248,7 +7310,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B27">
         <v>3.8080354659860869</v>
@@ -7260,7 +7322,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -7268,7 +7330,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B28">
         <v>0.35532273919989299</v>
@@ -7280,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -7288,7 +7350,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B29">
         <v>-1.252227383789952</v>
@@ -7300,7 +7362,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -7308,7 +7370,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B30">
         <v>2.7041046735015661</v>
@@ -7320,7 +7382,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -7328,7 +7390,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B31">
         <v>-1.009957488131532E-6</v>
@@ -7340,7 +7402,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -7348,7 +7410,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B32">
         <v>-0.7794457260989065</v>
@@ -7360,7 +7422,7 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -7368,7 +7430,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B33">
         <v>25.57077861162896</v>
@@ -7380,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -7388,7 +7450,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B34">
         <v>-24.403255810358889</v>
@@ -7400,7 +7462,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -7408,7 +7470,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B35">
         <v>25.596744189641111</v>
@@ -7420,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="G35" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -7428,7 +7490,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B36">
         <v>7.8653558859592498E-15</v>
@@ -7440,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -7448,7 +7510,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B37">
         <v>0.1140304863710548</v>
@@ -7460,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -7468,7 +7530,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B38">
         <v>1.367107440935978E-14</v>
@@ -7480,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -7488,7 +7550,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B39">
         <v>2.045221041526817E-3</v>
@@ -7500,7 +7562,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -7508,7 +7570,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B40">
         <v>1.462208659341158E-2</v>
@@ -7520,7 +7582,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -7528,7 +7590,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B41">
         <v>0.1174456015503173</v>
@@ -7540,7 +7602,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -7559,51 +7621,51 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B2">
         <v>2.999999002391656E-2</v>
@@ -7618,7 +7680,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H2">
         <v>-9.9760834385009822E-9</v>
@@ -7635,7 +7697,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B3">
         <v>-1.009957488131532E-6</v>
@@ -7653,7 +7715,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H3">
         <v>-9.9574881315319987E-9</v>
@@ -7673,7 +7735,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B4">
         <v>0.10000000992353759</v>
@@ -7688,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I4">
         <v>-9.9235375472517262E-9</v>
@@ -7705,7 +7767,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B5">
         <v>1.152921679642144</v>
@@ -7720,7 +7782,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H5">
         <v>-9.9892372151799691E-9</v>
@@ -7737,7 +7799,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B6">
         <v>-1.449605514745473E-16</v>
@@ -7755,7 +7817,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H6">
         <v>-1.449605514745473E-16</v>
@@ -7781,7 +7843,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B7">
         <v>-1.5253314907017229E-17</v>
@@ -7799,7 +7861,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H7">
         <v>-1.5253314907017229E-17</v>
@@ -7836,7 +7898,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7844,7 +7906,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B2">
         <v>25</v>
@@ -7852,7 +7914,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7860,7 +7922,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -7868,7 +7930,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -7876,7 +7938,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -7884,7 +7946,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -7892,7 +7954,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B8">
         <v>0.86474063979606752</v>
@@ -7900,7 +7962,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B9">
         <v>0.73917249775238103</v>
@@ -7908,7 +7970,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -7916,7 +7978,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B11">
         <v>0.87456361347890299</v>
@@ -7924,7 +7986,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -7932,7 +7994,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -7940,7 +8002,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B14">
         <v>0.38652020831194689</v>
@@ -7948,7 +8010,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -7956,7 +8018,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -7964,7 +8026,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -7972,7 +8034,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -7980,7 +8042,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B19">
         <v>0.9946446422596058</v>
@@ -7988,7 +8050,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -7996,7 +8058,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B21">
         <v>0.90208733793291584</v>
@@ -8004,7 +8066,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B22">
         <v>0.948906384805002</v>
@@ -8012,7 +8074,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B23">
         <v>0.46379233862769698</v>
@@ -8020,7 +8082,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B24">
         <v>0.18154350608052741</v>
@@ -8028,7 +8090,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -8036,7 +8098,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B26">
         <v>0.99921009814483686</v>
@@ -8044,7 +8106,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B27">
         <v>0.99995946131507929</v>
@@ -8052,7 +8114,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -8060,7 +8122,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -8068,7 +8130,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B30">
         <v>0.1619005956094198</v>
@@ -8076,7 +8138,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B31">
         <v>0.25</v>
@@ -8084,7 +8146,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -8092,7 +8154,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B33">
         <v>0.88784020448482548</v>
@@ -8100,7 +8162,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B34">
         <v>0.32579907703285982</v>
@@ -8108,7 +8170,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B35">
         <v>0.41613028762153992</v>
@@ -8116,7 +8178,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -8124,7 +8186,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -8132,7 +8194,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -8140,7 +8202,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B39">
         <v>0.76561702012764954</v>
@@ -8148,7 +8210,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B40">
         <v>0.1401002009618226</v>
@@ -8156,7 +8218,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B41">
         <v>0.91686100089898237</v>
@@ -8164,7 +8226,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -8172,7 +8234,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B43">
         <v>0.99497576916318042</v>
@@ -8180,7 +8242,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -8188,7 +8250,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -8196,7 +8258,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -8204,7 +8266,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B47">
         <v>0.14642792523039189</v>
@@ -8212,7 +8274,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B48">
         <v>0.53687697399136425</v>
@@ -8220,7 +8282,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B49">
         <v>0.67517152574500516</v>
@@ -8228,7 +8290,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B50">
         <v>0.14486639321675249</v>
@@ -8236,7 +8298,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B51">
         <v>0.78025334339286667</v>
@@ -8244,7 +8306,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B52">
         <v>0.73306805775703854</v>
@@ -8252,7 +8314,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B53">
         <v>0.74173420441284066</v>
@@ -8260,7 +8322,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B54">
         <v>0.94749321498430195</v>
@@ -8268,7 +8330,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -8276,7 +8338,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B56">
         <v>0.72729922161108951</v>
@@ -8284,7 +8346,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B57">
         <v>0.27395682656652642</v>
@@ -8292,7 +8354,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B58">
         <v>0.26331631400307459</v>
@@ -8300,7 +8362,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B59">
         <v>0.43825020768265749</v>
@@ -8308,7 +8370,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B60">
         <v>14.44066179802158</v>
@@ -8316,7 +8378,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B61">
         <v>0.90138981820586939</v>
@@ -8324,7 +8386,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B62">
         <v>8.0033242558760342</v>
@@ -8332,7 +8394,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B63">
         <v>7.0316502486194201</v>
@@ -8340,7 +8402,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B64">
         <v>3.0974512817869422</v>
@@ -8348,7 +8410,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B65">
         <v>2.647323773261252</v>
@@ -8356,7 +8418,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B66">
         <v>6.5445608991936073</v>
@@ -8364,7 +8426,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B67">
         <v>1.241831134209767</v>
@@ -8372,7 +8434,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B68">
         <v>0.6615890427732305</v>
@@ -8380,7 +8442,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B69">
         <v>0.15639610201537191</v>
@@ -8388,7 +8450,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B70">
         <v>2.9893214070905011E-3</v>
@@ -8396,7 +8458,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B71">
         <v>2.360239725177757E-4</v>
@@ -8404,7 +8466,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B72">
         <v>5.0883166565100573E-5</v>
@@ -8412,7 +8474,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B73">
         <v>81.818679050082253</v>
@@ -8420,7 +8482,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B74">
         <v>61.488136525307141</v>
@@ -8428,7 +8490,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B75">
         <v>48.392645424104963</v>
@@ -8436,7 +8498,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B76">
         <v>3.1814397827586229</v>
@@ -8444,7 +8506,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B77">
         <v>21.752235894525569</v>
@@ -8452,7 +8514,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B78">
         <v>0.51889766662216374</v>
@@ -8460,7 +8522,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B79">
         <v>7.1229657555937766</v>
@@ -8468,7 +8530,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B80">
         <v>5.4138563810845718E-2</v>
@@ -8476,7 +8538,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B81">
         <v>0.96333321972861941</v>
@@ -8484,7 +8546,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B82">
         <v>38495.338023949022</v>
@@ -8492,7 +8554,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B83">
         <v>24707.450154588059</v>
@@ -8500,7 +8562,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B84">
         <v>2.0209680979897331</v>
@@ -8508,7 +8570,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B85">
         <v>812.11364999091165</v>
@@ -8516,7 +8578,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B86">
         <v>66078.318558789935</v>
@@ -8524,7 +8586,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B87">
         <v>27198.59928900213</v>
@@ -8532,7 +8594,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B88">
         <v>0.3109831117427504</v>
@@ -8540,7 +8602,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B89">
         <v>2363.943369544606</v>
@@ -8548,7 +8610,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B90">
         <v>2.5449613374513009E-3</v>
@@ -8556,7 +8618,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B91">
         <v>475.95573441940752</v>
@@ -8564,7 +8626,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B92">
         <v>9.4647099322360972</v>
@@ -8572,7 +8634,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B93">
         <v>87.827885861302889</v>
@@ -8580,7 +8642,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B94">
         <v>1.2886715213733521E-4</v>
@@ -8588,7 +8650,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B95">
         <v>0.2502824035766622</v>
@@ -8596,7 +8658,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B96">
         <v>8.2079942842483433E-10</v>
@@ -8604,7 +8666,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B97">
         <v>1.111095312859023E-4</v>
@@ -8612,7 +8674,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B98">
         <v>4.6515569174232496E-12</v>
@@ -8620,7 +8682,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B99">
         <v>208.38546413766011</v>
@@ -8628,7 +8690,7 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B100">
         <v>213.47419545699421</v>
@@ -8636,7 +8698,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B101">
         <v>80.158658851462803</v>
@@ -8644,7 +8706,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B102">
         <v>310.58359887837878</v>
@@ -8652,7 +8714,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B103">
         <v>345.37459779538898</v>
@@ -8660,7 +8722,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B104">
         <v>655.22091851763707</v>
@@ -8668,7 +8730,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B105">
         <v>1106.7282824499341</v>
@@ -8676,7 +8738,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B106">
         <v>114.9964621143954</v>
@@ -8684,7 +8746,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B107">
         <v>0.88611845657025867</v>
@@ -8692,7 +8754,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B108">
         <v>9.649388412203308E-3</v>
@@ -8700,7 +8762,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B109">
         <v>1.039042229394127E-2</v>
@@ -8708,7 +8770,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B110">
         <v>4.6703587194480527E-2</v>
@@ -8716,7 +8778,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B111">
         <v>9.7449738497335403E-2</v>
@@ -8724,7 +8786,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B112">
         <v>0.16208606144989449</v>
@@ -8732,7 +8794,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B113">
         <v>0.20016579428919459</v>
@@ -8740,7 +8802,7 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B114">
         <v>4.2971822023927693E-2</v>
@@ -8748,7 +8810,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B115">
         <v>5.0531542403343011E-2</v>
@@ -8756,7 +8818,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B116">
         <v>1.1256168928113651E-2</v>
@@ -8764,7 +8826,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B117">
         <v>7.4631930968802607E-3</v>
@@ -8772,7 +8834,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B118">
         <v>0.81684970034910886</v>
@@ -8780,7 +8842,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B119">
         <v>1.8566858901269969E-3</v>
@@ -8788,7 +8850,7 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B120">
         <v>6.9043623827091949E-4</v>
@@ -8796,7 +8858,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B121">
         <v>1.5776119960619891E-5</v>
@@ -8804,7 +8866,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B122">
         <v>1.4239045498243291E-8</v>
@@ -8812,7 +8874,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B123">
         <v>6.0747851193809765E-11</v>
@@ -8820,7 +8882,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B124">
         <v>3.7461700408414338E-11</v>
@@ -8828,7 +8890,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B125">
         <v>0.70056030884530607</v>
@@ -8836,7 +8898,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B126">
         <v>0.42204810022735728</v>
@@ -8844,7 +8906,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B127">
         <v>0.32623562957338242</v>
@@ -8852,7 +8914,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B128">
         <v>0.29431007062317671</v>
@@ -8860,7 +8922,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B129">
         <v>6.2111171015125421E-2</v>
@@ -8868,7 +8930,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B130">
         <v>5.9551756691801572E-2</v>
@@ -8876,7 +8938,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B131">
         <v>1.6524327702663651E-2</v>
@@ -8884,7 +8946,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B132">
         <v>1.8670007590166899E-3</v>
@@ -8892,7 +8954,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -8900,7 +8962,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B134">
         <v>0.13073140821003959</v>
@@ -8908,7 +8970,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B135">
         <v>4.2750729001444839E-2</v>
@@ -8916,7 +8978,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B136">
         <v>1.019127528443889E-2</v>
@@ -8924,7 +8986,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B137">
         <v>2.3112428931271758E-2</v>
@@ -8932,7 +8994,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B138">
         <v>0.14793982769138331</v>
@@ -8940,7 +9002,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B139">
         <v>9.5495420111029752E-2</v>
@@ -8948,7 +9010,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B140">
         <v>2.865791805345809E-2</v>
@@ -8956,7 +9018,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B141">
         <v>9.6261890880453994E-3</v>
@@ -8964,7 +9026,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B142">
         <v>3.0982361624112892E-3</v>
@@ -8972,7 +9034,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B143">
         <v>1.0472652506331669E-3</v>
@@ -8980,7 +9042,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B144">
         <v>0.32314287621915799</v>
@@ -8988,7 +9050,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B145">
         <v>4.6103474462080428E-4</v>
@@ -8996,7 +9058,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B146">
         <v>5.1867754384928179E-5</v>
@@ -9004,7 +9066,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B147">
         <v>1.5545372974698261E-6</v>
@@ -9012,7 +9074,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B148">
         <v>1.224047284573878E-7</v>
@@ -9020,7 +9082,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B149">
         <v>1.6096462496243201E-8</v>
@@ -9028,7 +9090,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B150">
         <v>9.9999999999999994E-12</v>
@@ -9036,7 +9098,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B151">
         <v>1.889234020690886</v>
@@ -9044,7 +9106,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B152">
         <v>3.2196909736022472</v>
@@ -9052,7 +9114,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B153">
         <v>2.2213791143772821</v>
@@ -9060,7 +9122,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B154">
         <v>11.804197753506241</v>
@@ -9068,7 +9130,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B155">
         <v>1.571961546633907</v>
@@ -9076,7 +9138,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B156">
         <v>0.98668079456243907</v>
@@ -9084,7 +9146,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B157">
         <v>0.4240794036675688</v>
@@ -9092,7 +9154,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B158">
         <v>4.3359541493340252E-2</v>
@@ -9100,7 +9162,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B159">
         <v>3.53074955862377</v>
@@ -9108,7 +9170,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B160">
         <v>2.637440975102415</v>
@@ -9116,7 +9178,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B161">
         <v>2.6131938249850482</v>
@@ -9124,7 +9186,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B162">
         <v>2.5135033485776548</v>
@@ -9132,7 +9194,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B163">
         <v>2.311783831322646</v>
@@ -9140,7 +9202,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B164">
         <v>2.447641798908395</v>
@@ -9148,7 +9210,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B165">
         <v>2.259497200302917</v>
@@ -9156,7 +9218,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B166">
         <v>2.2568691565230581</v>
@@ -9164,7 +9226,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B167">
         <v>2.206202350443796</v>
@@ -9172,7 +9234,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B168">
         <v>2.1896104075685412</v>
@@ -9180,7 +9242,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B169">
         <v>2.173954280128013</v>
@@ -9188,7 +9250,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B170">
         <v>3.6991843242325788</v>
@@ -9196,7 +9258,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B171">
         <v>2.1685853065066811</v>
@@ -9204,7 +9266,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B172">
         <v>2.1665673801907328</v>
@@ -9212,7 +9274,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B173">
         <v>2.1662745440549029</v>
@@ -9220,7 +9282,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B174">
         <v>2.166268210231566</v>
@@ -9228,7 +9290,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B175">
         <v>2.166267507886781</v>
@@ -9236,7 +9298,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B176">
         <v>2.1662673950455948</v>
@@ -9244,7 +9306,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B177">
         <v>3.266075032891778</v>
@@ -9252,7 +9314,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B178">
         <v>3.224871879537706</v>
@@ -9260,7 +9322,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B179">
         <v>2.5600062914784329</v>
@@ -9268,7 +9330,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B180">
         <v>2.7115661685452421</v>
@@ -9276,7 +9338,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B181">
         <v>2.6123525062334072</v>
@@ -9284,7 +9346,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B182">
         <v>2.754337879639674</v>
@@ -9292,7 +9354,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B183">
         <v>2.6928844975419279</v>
@@ -9300,7 +9362,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B184">
         <v>2.6738217126259851</v>
@@ -9308,7 +9370,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -9316,7 +9378,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B186">
         <v>3.7037037037037028E-2</v>
@@ -9324,7 +9386,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B187">
         <v>9.8765432098765427E-2</v>
@@ -9332,7 +9394,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B188">
         <v>2.1069958847736618</v>
@@ -9340,7 +9402,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B189">
         <v>0.70233196159122069</v>
@@ -9348,7 +9410,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -9356,7 +9418,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B191">
         <v>0.23411065386374019</v>
@@ -9364,7 +9426,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -9372,7 +9434,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -9380,7 +9442,7 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -9388,7 +9450,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -9396,7 +9458,7 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -9404,7 +9466,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -9412,7 +9474,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -9420,7 +9482,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -9428,7 +9490,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -9436,7 +9498,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B201">
         <v>0</v>
@@ -9444,7 +9506,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B202">
         <v>0</v>
@@ -9452,7 +9514,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B203">
         <v>0</v>
@@ -9460,7 +9522,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B204">
         <v>0</v>
@@ -9468,7 +9530,7 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B205">
         <v>0</v>
@@ -9476,7 +9538,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -9484,7 +9546,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B207">
         <v>0</v>
@@ -9492,7 +9554,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B208">
         <v>0.33333333333333331</v>
@@ -9500,7 +9562,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B209">
         <v>0</v>
@@ -9508,7 +9570,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B210">
         <v>0.1111111111111111</v>
@@ -9516,7 +9578,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B211">
         <v>0</v>
@@ -9524,7 +9586,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B212">
         <v>37</v>
@@ -9532,7 +9594,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B213">
         <v>37</v>
@@ -9540,7 +9602,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B214">
         <v>0</v>
@@ -9548,7 +9610,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B215">
         <v>27</v>
@@ -9556,7 +9618,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B216">
         <v>25</v>
@@ -9564,7 +9626,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B217">
         <v>27</v>
@@ -9572,7 +9634,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -9580,15 +9642,15 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B219" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B220" t="b">
         <v>1</v>
@@ -9596,7 +9658,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B221">
         <v>0</v>
@@ -9604,7 +9666,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B222">
         <v>1.0610000000000011</v>
@@ -9612,7 +9674,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B223">
         <v>2.1579999999999999</v>
@@ -9620,7 +9682,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B224">
         <v>0</v>
@@ -9628,7 +9690,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B225">
         <v>1.732</v>
@@ -9636,7 +9698,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B226">
         <v>18.152999999999999</v>
@@ -9644,7 +9706,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B227">
         <v>6.0200000000000022</v>
@@ -9652,7 +9714,7 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B228">
         <v>29.221</v>
@@ -9660,7 +9722,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -9668,7 +9730,7 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B230">
         <v>1.063269</v>
@@ -9676,7 +9738,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B231">
         <v>2.1594120000000001</v>
@@ -9684,7 +9746,7 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -9692,7 +9754,7 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B233">
         <v>1.7313909999999999</v>
@@ -9700,7 +9762,7 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B234">
         <v>18.151599000000001</v>
@@ -9708,7 +9770,7 @@
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B235">
         <v>6.0192909999999999</v>
@@ -9716,7 +9778,7 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B236">
         <v>29.220783999999998</v>
@@ -9724,10 +9786,10 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B237" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -9743,19 +9805,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>618</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -9763,7 +9825,7 @@
         <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -9780,7 +9842,7 @@
         <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C3">
         <v>4.6988623620787158E-2</v>
@@ -9797,7 +9859,7 @@
         <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C4">
         <v>1.325917124942102E-2</v>
@@ -9814,7 +9876,7 @@
         <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C5">
         <v>2.1516069338430128</v>
@@ -9831,7 +9893,7 @@
         <v>116</v>
       </c>
       <c r="B6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C6">
         <v>7.8309183480030797E-2</v>
@@ -9848,7 +9910,7 @@
         <v>117</v>
       </c>
       <c r="B7" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C7">
         <v>0.24707337911315319</v>
@@ -9887,36 +9949,36 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B2">
         <v>3.8080354659860869</v>
@@ -9934,7 +9996,7 @@
         <v>1.2E-2</v>
       </c>
       <c r="G2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -9942,7 +10004,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B3">
         <v>7.8653558859592498E-15</v>
@@ -9960,7 +10022,7 @@
         <v>0.06</v>
       </c>
       <c r="G3" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -9968,7 +10030,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B4">
         <v>-0.1140304863710548</v>
@@ -9986,7 +10048,7 @@
         <v>0.06</v>
       </c>
       <c r="G4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -9994,7 +10056,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B5">
         <v>-1.367107440935978E-14</v>
@@ -10012,7 +10074,7 @@
         <v>0.06</v>
       </c>
       <c r="G5" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -10038,13 +10100,13 @@
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="G6" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -10067,7 +10129,7 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="G7" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
@@ -10075,7 +10137,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B8">
         <v>0.39999999440488571</v>
@@ -10093,13 +10155,13 @@
         <v>8.0000000000000004E-4</v>
       </c>
       <c r="G8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -10122,7 +10184,7 @@
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="G9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -10148,7 +10210,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="G10" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H10" t="b">
         <v>0</v>
@@ -10156,7 +10218,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B11">
         <v>0.1187676990826549</v>
@@ -10174,7 +10236,7 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="G11" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
